--- a/Table/addressable.xlsx
+++ b/Table/addressable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23400" windowHeight="10500"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>CS</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>SubAssets/ConfigBin</t>
@@ -753,7 +756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -773,9 +776,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1182,25 +1182,25 @@
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:4">
       <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>10</v>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -1213,8 +1213,8 @@
       <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>11</v>
+      <c r="B6" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -1227,8 +1227,8 @@
       <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
+      <c r="B7" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -1241,8 +1241,8 @@
       <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>13</v>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -1255,8 +1255,8 @@
       <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>14</v>
+      <c r="B9" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -1269,8 +1269,8 @@
       <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>15</v>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
@@ -1283,8 +1283,8 @@
       <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>16</v>
+      <c r="B11" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -1297,8 +1297,8 @@
       <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>17</v>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -1311,8 +1311,8 @@
       <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>18</v>
+      <c r="B13" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -1325,8 +1325,8 @@
       <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>19</v>
+      <c r="B14" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="C14" s="6">
         <v>2</v>
@@ -1339,8 +1339,8 @@
       <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>20</v>
+      <c r="B15" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="C15" s="6">
         <v>2</v>
@@ -1353,8 +1353,8 @@
       <c r="A16" s="3">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>21</v>
+      <c r="B16" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="C16" s="6">
         <v>2</v>
@@ -1367,8 +1367,8 @@
       <c r="A17" s="3">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>22</v>
+      <c r="B17" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C17" s="6">
         <v>2</v>
@@ -1381,8 +1381,8 @@
       <c r="A18" s="3">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>23</v>
+      <c r="B18" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="C18" s="6">
         <v>2</v>
@@ -1395,8 +1395,8 @@
       <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>24</v>
+      <c r="B19" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="6">
         <v>2</v>
@@ -1409,8 +1409,8 @@
       <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>25</v>
+      <c r="B20" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C20" s="6">
         <v>2</v>
@@ -1421,87 +1421,87 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:3">
       <c r="A21" s="3"/>
-      <c r="B21" s="8"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:3">
       <c r="A22" s="3"/>
-      <c r="B22" s="8"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="6"/>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:3">
       <c r="A23" s="3"/>
-      <c r="B23" s="8"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="6"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:3">
       <c r="A24" s="3"/>
-      <c r="B24" s="8"/>
+      <c r="B24" s="7"/>
       <c r="C24" s="6"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:3">
       <c r="A25" s="3"/>
-      <c r="B25" s="8"/>
+      <c r="B25" s="7"/>
       <c r="C25" s="6"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:3">
       <c r="A26" s="3"/>
-      <c r="B26" s="8"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="6"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:3">
       <c r="A27" s="3"/>
-      <c r="B27" s="8"/>
+      <c r="B27" s="7"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:3">
       <c r="A28" s="3"/>
-      <c r="B28" s="8"/>
+      <c r="B28" s="7"/>
       <c r="C28" s="6"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:3">
       <c r="A29" s="3"/>
-      <c r="B29" s="8"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="6"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:3">
       <c r="A30" s="3"/>
-      <c r="B30" s="8"/>
+      <c r="B30" s="7"/>
       <c r="C30" s="6"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:3">
       <c r="A31" s="3"/>
-      <c r="B31" s="8"/>
+      <c r="B31" s="7"/>
       <c r="C31" s="6"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:3">
       <c r="A32" s="3"/>
-      <c r="B32" s="8"/>
+      <c r="B32" s="7"/>
       <c r="C32" s="6"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
-      <c r="B33" s="8"/>
+      <c r="B33" s="7"/>
       <c r="C33" s="6"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:3">
       <c r="A34" s="3"/>
-      <c r="B34" s="8"/>
+      <c r="B34" s="7"/>
       <c r="C34" s="6"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:3">
       <c r="A35" s="3"/>
-      <c r="B35" s="8"/>
+      <c r="B35" s="7"/>
       <c r="C35" s="6"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:3">
       <c r="A36" s="3"/>
-      <c r="B36" s="8"/>
+      <c r="B36" s="7"/>
       <c r="C36" s="6"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:3">
       <c r="A37" s="3"/>
-      <c r="B37" s="8"/>
+      <c r="B37" s="7"/>
       <c r="C37" s="6"/>
     </row>
   </sheetData>

--- a/Table/addressable.xlsx
+++ b/Table/addressable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -46,6 +46,12 @@
 1:忽略的不创建Group</t>
   </si>
   <si>
+    <t>int数组</t>
+  </si>
+  <si>
+    <t>int二维数组</t>
+  </si>
+  <si>
     <t>Directory</t>
   </si>
   <si>
@@ -55,12 +61,24 @@
     <t>Ignore</t>
   </si>
   <si>
+    <t>intArr</t>
+  </si>
+  <si>
+    <t>towArr</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>int[][]</t>
+  </si>
+  <si>
     <t>CS</t>
   </si>
   <si>
@@ -70,49 +88,28 @@
     <t>SubAssets/ConfigBin</t>
   </si>
   <si>
+    <t>[1, 2, 3]</t>
+  </si>
+  <si>
+    <t>[[100, 1001],[1002,1003]]</t>
+  </si>
+  <si>
     <t>SubAssets/CSVAssets</t>
   </si>
   <si>
+    <t>[4, 5, 6]</t>
+  </si>
+  <si>
+    <t>[[1004, 1005],[1006,1007]]</t>
+  </si>
+  <si>
     <t>SubAssets/Res/Fonts</t>
   </si>
   <si>
-    <t>SubAssets/Res/Prefab/AddressableTest</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Prefab/Character</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Prefab/Collider</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Prefab/Labyrinth</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Prefab/Palette</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Prefab/Sound</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Prefab/UI</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Sound</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Spine/FrontRear</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Spine/Single</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/Sprite</t>
-  </si>
-  <si>
-    <t>SubAssets/Res/TileAsset</t>
-  </si>
-  <si>
-    <t>SubAssets/Scenes</t>
+    <t>[7, 8, 9]</t>
+  </si>
+  <si>
+    <t>[[1008, 1009],[1010,1011]]</t>
   </si>
 </sst>
 </file>
@@ -1129,17 +1126,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="60.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="45.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="13.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.25" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:4">
+    <row r="1" ht="40.5" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1152,55 +1151,79 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="25" customHeight="1" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1" spans="1:4">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1" spans="1:4">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:6">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -1208,13 +1231,19 @@
       <c r="D5" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" ht="25" customHeight="1" spans="1:4">
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:6">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -1222,13 +1251,19 @@
       <c r="D6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="25" customHeight="1" spans="1:4">
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:6">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -1236,188 +1271,77 @@
       <c r="D7" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="25" customHeight="1" spans="1:4">
-      <c r="A8" s="3">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1" spans="1:4">
-      <c r="A9" s="3">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1" spans="1:4">
-      <c r="A10" s="3">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1" spans="1:4">
-      <c r="A11" s="3">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1" spans="1:4">
-      <c r="A12" s="3">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1" spans="1:4">
-      <c r="A13" s="3">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1" spans="1:4">
-      <c r="A14" s="3">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1" spans="1:4">
-      <c r="A15" s="3">
-        <v>11</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1" spans="1:4">
-      <c r="A16" s="3">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1" spans="1:4">
-      <c r="A17" s="3">
-        <v>13</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1" spans="1:4">
-      <c r="A18" s="3">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="6">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1" spans="1:4">
-      <c r="A19" s="3">
-        <v>15</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="F7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="6">
-        <v>2</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1" spans="1:4">
-      <c r="A20" s="3">
-        <v>16</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" ht="25" customHeight="1" spans="1:3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" ht="25" customHeight="1" spans="1:3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" ht="25" customHeight="1" spans="1:3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" ht="25" customHeight="1" spans="1:3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:3">
       <c r="A21" s="3"/>
@@ -1438,71 +1362,6 @@
       <c r="A24" s="3"/>
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
-    </row>
-    <row r="25" ht="25" customHeight="1" spans="1:3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="6"/>
-    </row>
-    <row r="26" ht="25" customHeight="1" spans="1:3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="6"/>
-    </row>
-    <row r="27" ht="25" customHeight="1" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="6"/>
-    </row>
-    <row r="28" ht="25" customHeight="1" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" ht="25" customHeight="1" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" ht="25" customHeight="1" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="6"/>
-    </row>
-    <row r="31" ht="25" customHeight="1" spans="1:3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="6"/>
-    </row>
-    <row r="32" ht="25" customHeight="1" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" ht="25" customHeight="1" spans="1:3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="6"/>
-    </row>
-    <row r="34" ht="25" customHeight="1" spans="1:3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="6"/>
-    </row>
-    <row r="35" ht="25" customHeight="1" spans="1:3">
-      <c r="A35" s="3"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="6"/>
-    </row>
-    <row r="36" ht="25" customHeight="1" spans="1:3">
-      <c r="A36" s="3"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="6"/>
-    </row>
-    <row r="37" ht="25" customHeight="1" spans="1:3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
